--- a/artfynd/A 56483-2023 artfynd.xlsx
+++ b/artfynd/A 56483-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY12"/>
+  <dimension ref="A1:AY6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>115842172</v>
+        <v>115842239</v>
       </c>
       <c r="B2" t="n">
-        <v>77895</v>
+        <v>57265</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,26 +691,31 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6437</v>
+        <v>100109</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -718,10 +723,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>370475</v>
+        <v>370461</v>
       </c>
       <c r="R2" t="n">
-        <v>6928441</v>
+        <v>6928304</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -756,13 +761,17 @@
           <t>2024-03-29</t>
         </is>
       </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>ringhack färsk</t>
+        </is>
+      </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -781,10 +790,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>115842239</v>
+        <v>115842292</v>
       </c>
       <c r="B3" t="n">
-        <v>57265</v>
+        <v>78507</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -797,31 +806,26 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -829,10 +833,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>370461</v>
+        <v>370446</v>
       </c>
       <c r="R3" t="n">
-        <v>6928304</v>
+        <v>6928325</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -867,17 +871,13 @@
           <t>2024-03-29</t>
         </is>
       </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>ringhack färsk</t>
-        </is>
-      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -896,10 +896,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>115842038</v>
+        <v>115842286</v>
       </c>
       <c r="B4" t="n">
-        <v>74647</v>
+        <v>90332</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -912,21 +912,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6440</v>
+        <v>1202</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -939,10 +939,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>370551</v>
+        <v>370446</v>
       </c>
       <c r="R4" t="n">
-        <v>6928400</v>
+        <v>6928325</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -1002,10 +1002,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>115842176</v>
+        <v>115842263</v>
       </c>
       <c r="B5" t="n">
-        <v>78507</v>
+        <v>77446</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1018,21 +1018,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>6487</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1045,10 +1045,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>370475</v>
+        <v>370461</v>
       </c>
       <c r="R5" t="n">
-        <v>6928441</v>
+        <v>6928304</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1108,10 +1108,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>115842292</v>
+        <v>115842244</v>
       </c>
       <c r="B6" t="n">
-        <v>78507</v>
+        <v>77895</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1124,21 +1124,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>6437</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1151,10 +1151,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>370446</v>
+        <v>370461</v>
       </c>
       <c r="R6" t="n">
-        <v>6928325</v>
+        <v>6928304</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1211,650 +1211,6 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
-    </row>
-    <row r="7">
-      <c r="A7" t="n">
-        <v>115842286</v>
-      </c>
-      <c r="B7" t="n">
-        <v>90332</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E7" t="n">
-        <v>1202</v>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>Ullticka</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>Phellinidium ferrugineofuscum</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="N7" t="inlineStr"/>
-      <c r="P7" t="inlineStr">
-        <is>
-          <t>Urgnäset, Hjd</t>
-        </is>
-      </c>
-      <c r="Q7" t="n">
-        <v>370446</v>
-      </c>
-      <c r="R7" t="n">
-        <v>6928325</v>
-      </c>
-      <c r="S7" t="n">
-        <v>25</v>
-      </c>
-      <c r="T7" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U7" t="inlineStr">
-        <is>
-          <t>Härjedalen</t>
-        </is>
-      </c>
-      <c r="V7" t="inlineStr">
-        <is>
-          <t>Härjedalen</t>
-        </is>
-      </c>
-      <c r="W7" t="inlineStr">
-        <is>
-          <t>Tännäs</t>
-        </is>
-      </c>
-      <c r="Y7" t="inlineStr">
-        <is>
-          <t>2024-03-29</t>
-        </is>
-      </c>
-      <c r="AA7" t="inlineStr">
-        <is>
-          <t>2024-03-29</t>
-        </is>
-      </c>
-      <c r="AD7" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE7" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF7" t="inlineStr"/>
-      <c r="AG7" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT7" t="inlineStr"/>
-      <c r="AW7" t="inlineStr">
-        <is>
-          <t>Bjarne Tutturen</t>
-        </is>
-      </c>
-      <c r="AX7" t="inlineStr">
-        <is>
-          <t>Bjarne Tutturen</t>
-        </is>
-      </c>
-      <c r="AY7" t="inlineStr"/>
-    </row>
-    <row r="8">
-      <c r="A8" t="n">
-        <v>115842263</v>
-      </c>
-      <c r="B8" t="n">
-        <v>77446</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E8" t="n">
-        <v>6487</v>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>Blågrå svartspik</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>Chaenothecopsis fennica</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>(Laurila) Tibell</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
-      <c r="N8" t="inlineStr"/>
-      <c r="P8" t="inlineStr">
-        <is>
-          <t>Urgnäset, Hjd</t>
-        </is>
-      </c>
-      <c r="Q8" t="n">
-        <v>370461</v>
-      </c>
-      <c r="R8" t="n">
-        <v>6928304</v>
-      </c>
-      <c r="S8" t="n">
-        <v>25</v>
-      </c>
-      <c r="T8" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U8" t="inlineStr">
-        <is>
-          <t>Härjedalen</t>
-        </is>
-      </c>
-      <c r="V8" t="inlineStr">
-        <is>
-          <t>Härjedalen</t>
-        </is>
-      </c>
-      <c r="W8" t="inlineStr">
-        <is>
-          <t>Tännäs</t>
-        </is>
-      </c>
-      <c r="Y8" t="inlineStr">
-        <is>
-          <t>2024-03-29</t>
-        </is>
-      </c>
-      <c r="AA8" t="inlineStr">
-        <is>
-          <t>2024-03-29</t>
-        </is>
-      </c>
-      <c r="AD8" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE8" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF8" t="inlineStr"/>
-      <c r="AG8" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT8" t="inlineStr"/>
-      <c r="AW8" t="inlineStr">
-        <is>
-          <t>Bjarne Tutturen</t>
-        </is>
-      </c>
-      <c r="AX8" t="inlineStr">
-        <is>
-          <t>Bjarne Tutturen</t>
-        </is>
-      </c>
-      <c r="AY8" t="inlineStr"/>
-    </row>
-    <row r="9">
-      <c r="A9" t="n">
-        <v>115842129</v>
-      </c>
-      <c r="B9" t="n">
-        <v>57147</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E9" t="n">
-        <v>100011</v>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>Kungsörn</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>Aquila chrysaetos</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>förbiflygande</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr"/>
-      <c r="P9" t="inlineStr">
-        <is>
-          <t>Urgnäset, Hjd</t>
-        </is>
-      </c>
-      <c r="Q9" t="n">
-        <v>370510</v>
-      </c>
-      <c r="R9" t="n">
-        <v>6928419</v>
-      </c>
-      <c r="S9" t="n">
-        <v>100</v>
-      </c>
-      <c r="T9" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U9" t="inlineStr">
-        <is>
-          <t>Härjedalen</t>
-        </is>
-      </c>
-      <c r="V9" t="inlineStr">
-        <is>
-          <t>Härjedalen</t>
-        </is>
-      </c>
-      <c r="W9" t="inlineStr">
-        <is>
-          <t>Tännäs</t>
-        </is>
-      </c>
-      <c r="Y9" t="inlineStr">
-        <is>
-          <t>2024-03-29</t>
-        </is>
-      </c>
-      <c r="AA9" t="inlineStr">
-        <is>
-          <t>2024-03-29</t>
-        </is>
-      </c>
-      <c r="AD9" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE9" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG9" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT9" t="inlineStr"/>
-      <c r="AW9" t="inlineStr">
-        <is>
-          <t>Bjarne Tutturen</t>
-        </is>
-      </c>
-      <c r="AX9" t="inlineStr">
-        <is>
-          <t>Bjarne Tutturen</t>
-        </is>
-      </c>
-      <c r="AY9" t="inlineStr"/>
-    </row>
-    <row r="10">
-      <c r="A10" t="n">
-        <v>115842191</v>
-      </c>
-      <c r="B10" t="n">
-        <v>57372</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E10" t="n">
-        <v>103031</v>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>Lavskrika</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>Perisoreus infaustus</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>par i lämplig häckbiotop</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr"/>
-      <c r="P10" t="inlineStr">
-        <is>
-          <t>Urgnäset, Hjd</t>
-        </is>
-      </c>
-      <c r="Q10" t="n">
-        <v>370422</v>
-      </c>
-      <c r="R10" t="n">
-        <v>6928449</v>
-      </c>
-      <c r="S10" t="n">
-        <v>50</v>
-      </c>
-      <c r="T10" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U10" t="inlineStr">
-        <is>
-          <t>Härjedalen</t>
-        </is>
-      </c>
-      <c r="V10" t="inlineStr">
-        <is>
-          <t>Härjedalen</t>
-        </is>
-      </c>
-      <c r="W10" t="inlineStr">
-        <is>
-          <t>Tännäs</t>
-        </is>
-      </c>
-      <c r="Y10" t="inlineStr">
-        <is>
-          <t>2024-03-29</t>
-        </is>
-      </c>
-      <c r="AA10" t="inlineStr">
-        <is>
-          <t>2024-03-29</t>
-        </is>
-      </c>
-      <c r="AD10" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE10" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG10" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT10" t="inlineStr"/>
-      <c r="AW10" t="inlineStr">
-        <is>
-          <t>Bjarne Tutturen</t>
-        </is>
-      </c>
-      <c r="AX10" t="inlineStr">
-        <is>
-          <t>Bjarne Tutturen</t>
-        </is>
-      </c>
-      <c r="AY10" t="inlineStr"/>
-    </row>
-    <row r="11">
-      <c r="A11" t="n">
-        <v>115842244</v>
-      </c>
-      <c r="B11" t="n">
-        <v>77895</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E11" t="n">
-        <v>6437</v>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>Blanksvart spiklav</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>Calicium denigratum</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>(Vain.) Tibell</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
-      <c r="N11" t="inlineStr"/>
-      <c r="P11" t="inlineStr">
-        <is>
-          <t>Urgnäset, Hjd</t>
-        </is>
-      </c>
-      <c r="Q11" t="n">
-        <v>370461</v>
-      </c>
-      <c r="R11" t="n">
-        <v>6928304</v>
-      </c>
-      <c r="S11" t="n">
-        <v>25</v>
-      </c>
-      <c r="T11" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U11" t="inlineStr">
-        <is>
-          <t>Härjedalen</t>
-        </is>
-      </c>
-      <c r="V11" t="inlineStr">
-        <is>
-          <t>Härjedalen</t>
-        </is>
-      </c>
-      <c r="W11" t="inlineStr">
-        <is>
-          <t>Tännäs</t>
-        </is>
-      </c>
-      <c r="Y11" t="inlineStr">
-        <is>
-          <t>2024-03-29</t>
-        </is>
-      </c>
-      <c r="AA11" t="inlineStr">
-        <is>
-          <t>2024-03-29</t>
-        </is>
-      </c>
-      <c r="AD11" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE11" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF11" t="inlineStr"/>
-      <c r="AG11" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT11" t="inlineStr"/>
-      <c r="AW11" t="inlineStr">
-        <is>
-          <t>Bjarne Tutturen</t>
-        </is>
-      </c>
-      <c r="AX11" t="inlineStr">
-        <is>
-          <t>Bjarne Tutturen</t>
-        </is>
-      </c>
-      <c r="AY11" t="inlineStr"/>
-    </row>
-    <row r="12">
-      <c r="A12" t="n">
-        <v>115842045</v>
-      </c>
-      <c r="B12" t="n">
-        <v>82248</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E12" t="n">
-        <v>1312</v>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>Gammelgransskål</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>Pseudographis pinicola</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>(Nyl.) Rehm</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
-      <c r="N12" t="inlineStr"/>
-      <c r="P12" t="inlineStr">
-        <is>
-          <t>Urgnäset, Hjd</t>
-        </is>
-      </c>
-      <c r="Q12" t="n">
-        <v>370551</v>
-      </c>
-      <c r="R12" t="n">
-        <v>6928400</v>
-      </c>
-      <c r="S12" t="n">
-        <v>25</v>
-      </c>
-      <c r="T12" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U12" t="inlineStr">
-        <is>
-          <t>Härjedalen</t>
-        </is>
-      </c>
-      <c r="V12" t="inlineStr">
-        <is>
-          <t>Härjedalen</t>
-        </is>
-      </c>
-      <c r="W12" t="inlineStr">
-        <is>
-          <t>Tännäs</t>
-        </is>
-      </c>
-      <c r="Y12" t="inlineStr">
-        <is>
-          <t>2024-03-29</t>
-        </is>
-      </c>
-      <c r="AA12" t="inlineStr">
-        <is>
-          <t>2024-03-29</t>
-        </is>
-      </c>
-      <c r="AD12" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE12" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF12" t="inlineStr"/>
-      <c r="AG12" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT12" t="inlineStr"/>
-      <c r="AW12" t="inlineStr">
-        <is>
-          <t>Bjarne Tutturen</t>
-        </is>
-      </c>
-      <c r="AX12" t="inlineStr">
-        <is>
-          <t>Bjarne Tutturen</t>
-        </is>
-      </c>
-      <c r="AY12" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 56483-2023 artfynd.xlsx
+++ b/artfynd/A 56483-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AY7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>115842239</v>
+        <v>115842286</v>
       </c>
       <c r="B2" t="n">
-        <v>57265</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,31 +686,26 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -723,10 +713,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>370461</v>
+        <v>370446</v>
       </c>
       <c r="R2" t="n">
-        <v>6928304</v>
+        <v>6928325</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -761,17 +751,13 @@
           <t>2024-03-29</t>
         </is>
       </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>ringhack färsk</t>
-        </is>
-      </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -793,16 +779,11 @@
         <v>115842292</v>
       </c>
       <c r="B3" t="n">
-        <v>78507</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
@@ -896,15 +877,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>115842286</v>
+        <v>115842244</v>
       </c>
       <c r="B4" t="n">
-        <v>90332</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78730</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -912,21 +888,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1202</v>
+        <v>6437</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -939,10 +915,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>370446</v>
+        <v>370461</v>
       </c>
       <c r="R4" t="n">
-        <v>6928325</v>
+        <v>6928304</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -1005,12 +981,7 @@
         <v>115842263</v>
       </c>
       <c r="B5" t="n">
-        <v>77446</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78334</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1108,15 +1079,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>115842244</v>
+        <v>115842239</v>
       </c>
       <c r="B6" t="n">
-        <v>77895</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1124,26 +1090,31 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6437</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1189,13 +1160,17 @@
           <t>2024-03-29</t>
         </is>
       </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>ringhack färsk</t>
+        </is>
+      </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1211,6 +1186,107 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>115842206</v>
+      </c>
+      <c r="B7" t="n">
+        <v>79917</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Urgnäset, Hjd</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>370519</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6928326</v>
+      </c>
+      <c r="S7" t="n">
+        <v>25</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Tännäs</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2024-03-29</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2024-03-29</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF7" t="inlineStr"/>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Bjarne Tutturen</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Bjarne Tutturen</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 56483-2023 artfynd.xlsx
+++ b/artfynd/A 56483-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY7"/>
+  <dimension ref="A1:AZ7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -773,6 +778,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115842286</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -874,6 +884,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115842292</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -975,6 +990,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115842244</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1076,6 +1096,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115842263</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1186,6 +1211,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115842239</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1287,8 +1317,21 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115842206</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>